--- a/excel_routes/route_CAI_TUU_threats.xlsx
+++ b/excel_routes/route_CAI_TUU_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D54E38F1-C609-4028-95B7-B3FD2CF3E3A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6138AF80-8AD7-4210-9D69-FE855733A9CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="601" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -66,64 +66,64 @@
     <t>SM-325</t>
   </si>
   <si>
+    <t>Nile Air NP-207</t>
+  </si>
+  <si>
+    <t>LOW</t>
+  </si>
+  <si>
+    <t>EGP</t>
+  </si>
+  <si>
+    <t>Nesma Airlines NE-122</t>
+  </si>
+  <si>
     <t>EgyptAir MS-811</t>
   </si>
   <si>
     <t>MED</t>
   </si>
   <si>
-    <t>EGP</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-122</t>
-  </si>
-  <si>
-    <t>LOW</t>
-  </si>
-  <si>
-    <t>Nile Air NP-207</t>
-  </si>
-  <si>
     <t>30-JUL-26</t>
   </si>
   <si>
     <t>31-JUL-26</t>
   </si>
   <si>
+    <t>Nesma Airlines NE-120</t>
+  </si>
+  <si>
+    <t>06-AUG-26</t>
+  </si>
+  <si>
+    <t>11-AUG-26</t>
+  </si>
+  <si>
+    <t>13-AUG-26</t>
+  </si>
+  <si>
+    <t>14-AUG-26</t>
+  </si>
+  <si>
+    <t>Nile Air NP-307</t>
+  </si>
+  <si>
+    <t>15-AUG-26</t>
+  </si>
+  <si>
+    <t>18-AUG-26</t>
+  </si>
+  <si>
+    <t>20-AUG-26</t>
+  </si>
+  <si>
+    <t>Air Arabia Egypt E5-599</t>
+  </si>
+  <si>
+    <t>21-AUG-26</t>
+  </si>
+  <si>
     <t>Nile Air NP-107</t>
-  </si>
-  <si>
-    <t>Nesma Airlines NE-120</t>
-  </si>
-  <si>
-    <t>08-AUG-26</t>
-  </si>
-  <si>
-    <t>11-AUG-26</t>
-  </si>
-  <si>
-    <t>13-AUG-26</t>
-  </si>
-  <si>
-    <t>14-AUG-26</t>
-  </si>
-  <si>
-    <t>Nile Air NP-307</t>
-  </si>
-  <si>
-    <t>15-AUG-26</t>
-  </si>
-  <si>
-    <t>18-AUG-26</t>
-  </si>
-  <si>
-    <t>20-AUG-26</t>
-  </si>
-  <si>
-    <t>Air Arabia Egypt E5-599</t>
-  </si>
-  <si>
-    <t>21-AUG-26</t>
   </si>
   <si>
     <t>22-AUG-26</t>
@@ -264,14 +264,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF3CD"/>
-        <bgColor rgb="FFFFF3CD"/>
+        <fgColor rgb="FFD4EDDA"/>
+        <bgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD4EDDA"/>
-        <bgColor rgb="FFD4EDDA"/>
+        <fgColor rgb="FFFFF3CD"/>
+        <bgColor rgb="FFFFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -628,7 +628,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K119"/>
+  <dimension ref="A1:K118"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -689,22 +689,22 @@
         <v>13</v>
       </c>
       <c r="D2" s="2">
-        <v>7891</v>
+        <v>8860</v>
       </c>
       <c r="E2" s="2">
         <v>10553</v>
       </c>
       <c r="F2" s="2">
-        <v>-2662</v>
+        <v>-1693</v>
       </c>
       <c r="G2" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H2" s="2">
         <v>30</v>
       </c>
       <c r="I2" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
         <v>14</v>
@@ -724,13 +724,13 @@
         <v>16</v>
       </c>
       <c r="D3" s="2">
-        <v>10389</v>
+        <v>9542</v>
       </c>
       <c r="E3" s="2">
         <v>10553</v>
       </c>
       <c r="F3" s="2">
-        <v>-164</v>
+        <v>-1011</v>
       </c>
       <c r="G3" s="2">
         <v>30</v>
@@ -741,8 +741,8 @@
       <c r="I3" s="2">
         <v>0</v>
       </c>
-      <c r="J3" s="4" t="s">
-        <v>17</v>
+      <c r="J3" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K3" s="2" t="s">
         <v>15</v>
@@ -756,28 +756,28 @@
         <v>12</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D4" s="2">
-        <v>10389</v>
+        <v>9897</v>
       </c>
       <c r="E4" s="2">
         <v>10553</v>
       </c>
       <c r="F4" s="2">
-        <v>-164</v>
+        <v>-656</v>
       </c>
       <c r="G4" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2">
         <v>30</v>
       </c>
       <c r="I4" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J4" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>15</v>
@@ -791,25 +791,25 @@
         <v>12</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="D5" s="2">
-        <v>8833</v>
+        <v>10389</v>
       </c>
       <c r="E5" s="2">
-        <v>10553</v>
+        <v>11549</v>
       </c>
       <c r="F5" s="2">
-        <v>-1720</v>
+        <v>-1160</v>
       </c>
       <c r="G5" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H5" s="2">
         <v>30</v>
       </c>
       <c r="I5" s="2">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J5" s="3" t="s">
         <v>14</v>
@@ -826,16 +826,16 @@
         <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D6" s="2">
         <v>10389</v>
       </c>
       <c r="E6" s="2">
-        <v>10553</v>
+        <v>11549</v>
       </c>
       <c r="F6" s="2">
-        <v>-164</v>
+        <v>-1160</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -846,8 +846,8 @@
       <c r="I6" s="2">
         <v>0</v>
       </c>
-      <c r="J6" s="4" t="s">
-        <v>17</v>
+      <c r="J6" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K6" s="2" t="s">
         <v>15</v>
@@ -855,13 +855,13 @@
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="D7" s="2">
         <v>10389</v>
@@ -881,8 +881,8 @@
       <c r="I7" s="2">
         <v>0</v>
       </c>
-      <c r="J7" s="4" t="s">
-        <v>17</v>
+      <c r="J7" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>15</v>
@@ -890,22 +890,22 @@
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="D8" s="2">
-        <v>10007</v>
+        <v>8546</v>
       </c>
       <c r="E8" s="2">
-        <v>10553</v>
+        <v>8559</v>
       </c>
       <c r="F8" s="2">
-        <v>-546</v>
+        <v>-13</v>
       </c>
       <c r="G8" s="2">
         <v>30</v>
@@ -916,8 +916,8 @@
       <c r="I8" s="2">
         <v>0</v>
       </c>
-      <c r="J8" s="4" t="s">
-        <v>17</v>
+      <c r="J8" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>15</v>
@@ -925,13 +925,13 @@
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D9" s="2">
         <v>10389</v>
@@ -951,8 +951,8 @@
       <c r="I9" s="2">
         <v>0</v>
       </c>
-      <c r="J9" s="4" t="s">
-        <v>17</v>
+      <c r="J9" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K9" s="2" t="s">
         <v>15</v>
@@ -966,16 +966,16 @@
         <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D10" s="2">
         <v>10389</v>
       </c>
       <c r="E10" s="2">
-        <v>11549</v>
+        <v>10553</v>
       </c>
       <c r="F10" s="2">
-        <v>-1160</v>
+        <v>-164</v>
       </c>
       <c r="G10" s="2">
         <v>30</v>
@@ -986,8 +986,8 @@
       <c r="I10" s="2">
         <v>0</v>
       </c>
-      <c r="J10" s="4" t="s">
-        <v>17</v>
+      <c r="J10" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>15</v>
@@ -1001,16 +1001,16 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
         <v>10389</v>
       </c>
       <c r="E11" s="2">
-        <v>10553</v>
+        <v>11549</v>
       </c>
       <c r="F11" s="2">
-        <v>-164</v>
+        <v>-1160</v>
       </c>
       <c r="G11" s="2">
         <v>30</v>
@@ -1021,8 +1021,8 @@
       <c r="I11" s="2">
         <v>0</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>17</v>
+      <c r="J11" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -1036,16 +1036,16 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D12" s="2">
-        <v>10389</v>
+        <v>11044</v>
       </c>
       <c r="E12" s="2">
-        <v>10553</v>
+        <v>11549</v>
       </c>
       <c r="F12" s="2">
-        <v>-164</v>
+        <v>-505</v>
       </c>
       <c r="G12" s="2">
         <v>30</v>
@@ -1056,8 +1056,8 @@
       <c r="I12" s="2">
         <v>0</v>
       </c>
-      <c r="J12" s="4" t="s">
-        <v>17</v>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -1071,16 +1071,16 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="D13" s="2">
         <v>10389</v>
       </c>
       <c r="E13" s="2">
-        <v>10553</v>
+        <v>11549</v>
       </c>
       <c r="F13" s="2">
-        <v>-164</v>
+        <v>-1160</v>
       </c>
       <c r="G13" s="2">
         <v>30</v>
@@ -1091,8 +1091,8 @@
       <c r="I13" s="2">
         <v>0</v>
       </c>
-      <c r="J13" s="4" t="s">
-        <v>17</v>
+      <c r="J13" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1100,22 +1100,22 @@
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D14" s="2">
-        <v>10389</v>
+        <v>12587</v>
       </c>
       <c r="E14" s="2">
-        <v>11549</v>
+        <v>17037</v>
       </c>
       <c r="F14" s="2">
-        <v>-1160</v>
+        <v>-4450</v>
       </c>
       <c r="G14" s="2">
         <v>30</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K14" s="2" t="s">
         <v>15</v>
@@ -1141,16 +1141,16 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D15" s="2">
-        <v>16505</v>
+        <v>12491</v>
       </c>
       <c r="E15" s="2">
-        <v>17038</v>
+        <v>12546</v>
       </c>
       <c r="F15" s="2">
-        <v>-533</v>
+        <v>-55</v>
       </c>
       <c r="G15" s="2">
         <v>30</v>
@@ -1161,8 +1161,8 @@
       <c r="I15" s="2">
         <v>0</v>
       </c>
-      <c r="J15" s="4" t="s">
-        <v>17</v>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>15</v>
@@ -1176,28 +1176,28 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D16" s="2">
-        <v>12491</v>
+        <v>13861</v>
       </c>
       <c r="E16" s="2">
-        <v>12546</v>
+        <v>15536</v>
       </c>
       <c r="F16" s="2">
-        <v>-55</v>
+        <v>-1675</v>
       </c>
       <c r="G16" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>0</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K16" s="2" t="s">
         <v>15</v>
@@ -1205,34 +1205,34 @@
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D17" s="2">
-        <v>13916</v>
+        <v>13952</v>
       </c>
       <c r="E17" s="2">
         <v>15536</v>
       </c>
       <c r="F17" s="2">
-        <v>-1620</v>
+        <v>-1584</v>
       </c>
       <c r="G17" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H17" s="2">
         <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>10</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>15</v>
@@ -1240,22 +1240,22 @@
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D18" s="2">
-        <v>13952</v>
+        <v>13979</v>
       </c>
       <c r="E18" s="2">
         <v>15536</v>
       </c>
       <c r="F18" s="2">
-        <v>-1584</v>
+        <v>-1557</v>
       </c>
       <c r="G18" s="2">
         <v>30</v>
@@ -1266,8 +1266,8 @@
       <c r="I18" s="2">
         <v>0</v>
       </c>
-      <c r="J18" s="4" t="s">
-        <v>17</v>
+      <c r="J18" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K18" s="2" t="s">
         <v>15</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D19" s="2">
-        <v>13979</v>
+        <v>13952</v>
       </c>
       <c r="E19" s="2">
-        <v>15536</v>
+        <v>14047</v>
       </c>
       <c r="F19" s="2">
-        <v>-1557</v>
+        <v>-95</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1301,8 +1301,8 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
+      <c r="J19" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1310,22 +1310,22 @@
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="D20" s="2">
         <v>13952</v>
       </c>
       <c r="E20" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F20" s="2">
-        <v>-96</v>
+        <v>-95</v>
       </c>
       <c r="G20" s="2">
         <v>30</v>
@@ -1336,8 +1336,8 @@
       <c r="I20" s="2">
         <v>0</v>
       </c>
-      <c r="J20" s="4" t="s">
-        <v>17</v>
+      <c r="J20" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>15</v>
@@ -1345,22 +1345,22 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
         <v>13952</v>
       </c>
       <c r="E21" s="2">
-        <v>14048</v>
+        <v>17037</v>
       </c>
       <c r="F21" s="2">
-        <v>-96</v>
+        <v>-3085</v>
       </c>
       <c r="G21" s="2">
         <v>30</v>
@@ -1372,7 +1372,7 @@
         <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>15</v>
@@ -1386,25 +1386,25 @@
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D22" s="2">
-        <v>13952</v>
+        <v>19413</v>
       </c>
       <c r="E22" s="2">
-        <v>17038</v>
+        <v>17037</v>
       </c>
       <c r="F22" s="2">
-        <v>-3086</v>
+        <v>2376</v>
       </c>
       <c r="G22" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="3" t="s">
         <v>14</v>
@@ -1415,22 +1415,22 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D23" s="2">
-        <v>19413</v>
+        <v>10935</v>
       </c>
       <c r="E23" s="2">
-        <v>17038</v>
+        <v>14047</v>
       </c>
       <c r="F23" s="2">
-        <v>2375</v>
+        <v>-3112</v>
       </c>
       <c r="G23" s="2">
         <v>46</v>
@@ -1441,8 +1441,8 @@
       <c r="I23" s="2">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="s">
-        <v>17</v>
+      <c r="J23" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>15</v>
@@ -1456,28 +1456,28 @@
         <v>12</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>13</v>
+        <v>26</v>
       </c>
       <c r="D24" s="2">
-        <v>10935</v>
+        <v>10962</v>
       </c>
       <c r="E24" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F24" s="2">
-        <v>-3113</v>
+        <v>-3085</v>
       </c>
       <c r="G24" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2">
         <v>30</v>
       </c>
       <c r="I24" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K24" s="2" t="s">
         <v>15</v>
@@ -1491,16 +1491,16 @@
         <v>12</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D25" s="2">
         <v>10962</v>
       </c>
       <c r="E25" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F25" s="2">
-        <v>-3086</v>
+        <v>-3085</v>
       </c>
       <c r="G25" s="2">
         <v>30</v>
@@ -1511,8 +1511,8 @@
       <c r="I25" s="2">
         <v>0</v>
       </c>
-      <c r="J25" s="3" t="s">
-        <v>14</v>
+      <c r="J25" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>15</v>
@@ -1526,28 +1526,28 @@
         <v>12</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D26" s="2">
+        <v>11044</v>
+      </c>
+      <c r="E26" s="2">
+        <v>14047</v>
+      </c>
+      <c r="F26" s="2">
+        <v>-3003</v>
+      </c>
+      <c r="G26" s="2">
+        <v>30</v>
+      </c>
+      <c r="H26" s="2">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2">
+        <v>0</v>
+      </c>
+      <c r="J26" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D26" s="2">
-        <v>10962</v>
-      </c>
-      <c r="E26" s="2">
-        <v>14048</v>
-      </c>
-      <c r="F26" s="2">
-        <v>-3086</v>
-      </c>
-      <c r="G26" s="2">
-        <v>30</v>
-      </c>
-      <c r="H26" s="2">
-        <v>30</v>
-      </c>
-      <c r="I26" s="2">
-        <v>0</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K26" s="2" t="s">
         <v>15</v>
@@ -1555,34 +1555,34 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27" s="2">
-        <v>11044</v>
+        <v>10580</v>
       </c>
       <c r="E27" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F27" s="2">
-        <v>-3004</v>
+        <v>-3467</v>
       </c>
       <c r="G27" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2">
         <v>30</v>
       </c>
       <c r="I27" s="2">
-        <v>0</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>14</v>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>15</v>
@@ -1599,25 +1599,25 @@
         <v>13</v>
       </c>
       <c r="D28" s="2">
-        <v>10580</v>
+        <v>10962</v>
       </c>
       <c r="E28" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F28" s="2">
-        <v>-3468</v>
+        <v>-3085</v>
       </c>
       <c r="G28" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H28" s="2">
         <v>30</v>
       </c>
       <c r="I28" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K28" s="2" t="s">
         <v>15</v>
@@ -1637,10 +1637,10 @@
         <v>10962</v>
       </c>
       <c r="E29" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F29" s="2">
-        <v>-3086</v>
+        <v>-3085</v>
       </c>
       <c r="G29" s="2">
         <v>30</v>
@@ -1651,8 +1651,8 @@
       <c r="I29" s="2">
         <v>0</v>
       </c>
-      <c r="J29" s="3" t="s">
-        <v>14</v>
+      <c r="J29" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K29" s="2" t="s">
         <v>15</v>
@@ -1672,10 +1672,10 @@
         <v>11044</v>
       </c>
       <c r="E30" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F30" s="2">
-        <v>-3004</v>
+        <v>-3003</v>
       </c>
       <c r="G30" s="2">
         <v>30</v>
@@ -1686,8 +1686,8 @@
       <c r="I30" s="2">
         <v>0</v>
       </c>
-      <c r="J30" s="3" t="s">
-        <v>14</v>
+      <c r="J30" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>15</v>
@@ -1701,16 +1701,16 @@
         <v>12</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D31" s="2">
-        <v>11254</v>
+        <v>11209</v>
       </c>
       <c r="E31" s="2">
-        <v>14048</v>
+        <v>14047</v>
       </c>
       <c r="F31" s="2">
-        <v>-2794</v>
+        <v>-2838</v>
       </c>
       <c r="G31" s="2">
         <v>20</v>
@@ -1721,8 +1721,8 @@
       <c r="I31" s="2">
         <v>10</v>
       </c>
-      <c r="J31" s="4" t="s">
-        <v>17</v>
+      <c r="J31" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>15</v>
@@ -1730,34 +1730,34 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C32" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="2">
+        <v>11262</v>
+      </c>
+      <c r="E32" s="2">
+        <v>15536</v>
+      </c>
+      <c r="F32" s="2">
+        <v>-4274</v>
+      </c>
+      <c r="G32" s="2">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2">
+        <v>0</v>
+      </c>
+      <c r="J32" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D32" s="2">
-        <v>11263</v>
-      </c>
-      <c r="E32" s="2">
-        <v>14048</v>
-      </c>
-      <c r="F32" s="2">
-        <v>-2785</v>
-      </c>
-      <c r="G32" s="2">
-        <v>30</v>
-      </c>
-      <c r="H32" s="2">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2">
-        <v>0</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K32" s="2" t="s">
         <v>15</v>
@@ -1771,16 +1771,16 @@
         <v>12</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D33" s="2">
-        <v>11263</v>
+        <v>11262</v>
       </c>
       <c r="E33" s="2">
         <v>15536</v>
       </c>
       <c r="F33" s="2">
-        <v>-4273</v>
+        <v>-4274</v>
       </c>
       <c r="G33" s="2">
         <v>30</v>
@@ -1791,8 +1791,8 @@
       <c r="I33" s="2">
         <v>0</v>
       </c>
-      <c r="J33" s="3" t="s">
-        <v>14</v>
+      <c r="J33" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>15</v>
@@ -1806,16 +1806,16 @@
         <v>12</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D34" s="2">
-        <v>11331</v>
+        <v>11286</v>
       </c>
       <c r="E34" s="2">
         <v>15536</v>
       </c>
       <c r="F34" s="2">
-        <v>-4205</v>
+        <v>-4250</v>
       </c>
       <c r="G34" s="2">
         <v>20</v>
@@ -1827,7 +1827,7 @@
         <v>10</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K34" s="2" t="s">
         <v>15</v>
@@ -1835,34 +1835,34 @@
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D35" s="2">
-        <v>13952</v>
+        <v>10580</v>
       </c>
       <c r="E35" s="2">
         <v>15536</v>
       </c>
       <c r="F35" s="2">
-        <v>-1584</v>
+        <v>-4956</v>
       </c>
       <c r="G35" s="2">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2">
         <v>30</v>
       </c>
       <c r="I35" s="2">
-        <v>0</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>17</v>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>15</v>
@@ -1879,25 +1879,25 @@
         <v>13</v>
       </c>
       <c r="D36" s="2">
-        <v>10580</v>
+        <v>11262</v>
       </c>
       <c r="E36" s="2">
         <v>15536</v>
       </c>
       <c r="F36" s="2">
-        <v>-4956</v>
+        <v>-4274</v>
       </c>
       <c r="G36" s="2">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2">
         <v>30</v>
       </c>
       <c r="I36" s="2">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K36" s="2" t="s">
         <v>15</v>
@@ -1905,34 +1905,34 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="2">
+        <v>9774</v>
+      </c>
+      <c r="E37" s="2">
+        <v>18525</v>
+      </c>
+      <c r="F37" s="2">
+        <v>-8751</v>
+      </c>
+      <c r="G37" s="2">
+        <v>0</v>
+      </c>
+      <c r="H37" s="2">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2">
+        <v>30</v>
+      </c>
+      <c r="J37" s="4" t="s">
         <v>18</v>
-      </c>
-      <c r="D37" s="2">
-        <v>11263</v>
-      </c>
-      <c r="E37" s="2">
-        <v>15536</v>
-      </c>
-      <c r="F37" s="2">
-        <v>-4273</v>
-      </c>
-      <c r="G37" s="2">
-        <v>30</v>
-      </c>
-      <c r="H37" s="2">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>14</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>15</v>
@@ -1949,25 +1949,25 @@
         <v>13</v>
       </c>
       <c r="D38" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E38" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F38" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G38" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H38" s="2">
         <v>30</v>
       </c>
       <c r="I38" s="2">
-        <v>30</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J38" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K38" s="2" t="s">
         <v>15</v>
@@ -1981,16 +1981,16 @@
         <v>12</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D39" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E39" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F39" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G39" s="2">
         <v>30</v>
@@ -2010,31 +2010,31 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D40" s="2">
-        <v>10389</v>
+        <v>9449</v>
       </c>
       <c r="E40" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F40" s="2">
-        <v>-8137</v>
+        <v>-9076</v>
       </c>
       <c r="G40" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H40" s="2">
         <v>30</v>
       </c>
       <c r="I40" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J40" s="5" t="s">
         <v>35</v>
@@ -2051,28 +2051,28 @@
         <v>12</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D41" s="2">
-        <v>9487</v>
+        <v>9774</v>
       </c>
       <c r="E41" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F41" s="2">
-        <v>-9039</v>
+        <v>-8751</v>
       </c>
       <c r="G41" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H41" s="2">
         <v>30</v>
       </c>
       <c r="I41" s="2">
-        <v>10</v>
-      </c>
-      <c r="J41" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J41" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K41" s="2" t="s">
         <v>15</v>
@@ -2089,25 +2089,25 @@
         <v>13</v>
       </c>
       <c r="D42" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E42" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F42" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G42" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H42" s="2">
         <v>30</v>
       </c>
       <c r="I42" s="2">
-        <v>30</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J42" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K42" s="2" t="s">
         <v>15</v>
@@ -2121,16 +2121,16 @@
         <v>12</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D43" s="2">
-        <v>10007</v>
+        <v>11044</v>
       </c>
       <c r="E43" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F43" s="2">
-        <v>-8519</v>
+        <v>-7481</v>
       </c>
       <c r="G43" s="2">
         <v>30</v>
@@ -2150,31 +2150,31 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D44" s="2">
-        <v>11044</v>
+        <v>9525</v>
       </c>
       <c r="E44" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F44" s="2">
-        <v>-7482</v>
+        <v>-9000</v>
       </c>
       <c r="G44" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H44" s="2">
         <v>30</v>
       </c>
       <c r="I44" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J44" s="5" t="s">
         <v>35</v>
@@ -2191,25 +2191,25 @@
         <v>12</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D45" s="2">
-        <v>9564</v>
+        <v>10006</v>
       </c>
       <c r="E45" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F45" s="2">
-        <v>-8962</v>
+        <v>-8519</v>
       </c>
       <c r="G45" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2">
         <v>30</v>
       </c>
       <c r="I45" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J45" s="5" t="s">
         <v>35</v>
@@ -2226,13 +2226,13 @@
         <v>12</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D46" s="2">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="E46" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F46" s="2">
         <v>-8519</v>
@@ -2264,13 +2264,13 @@
         <v>21</v>
       </c>
       <c r="D47" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E47" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F47" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G47" s="2">
         <v>30</v>
@@ -2290,34 +2290,34 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D48" s="2">
-        <v>10389</v>
+        <v>9774</v>
       </c>
       <c r="E48" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F48" s="2">
-        <v>-8137</v>
+        <v>-8751</v>
       </c>
       <c r="G48" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H48" s="2">
         <v>30</v>
       </c>
       <c r="I48" s="2">
-        <v>0</v>
-      </c>
-      <c r="J48" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K48" s="2" t="s">
         <v>15</v>
@@ -2334,25 +2334,25 @@
         <v>13</v>
       </c>
       <c r="D49" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E49" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F49" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G49" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2">
         <v>30</v>
       </c>
       <c r="I49" s="2">
-        <v>30</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J49" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K49" s="2" t="s">
         <v>15</v>
@@ -2366,16 +2366,16 @@
         <v>12</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D50" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E50" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F50" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G50" s="2">
         <v>30</v>
@@ -2395,34 +2395,34 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D51" s="2">
-        <v>10389</v>
+        <v>9774</v>
       </c>
       <c r="E51" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F51" s="2">
-        <v>-8137</v>
+        <v>-8751</v>
       </c>
       <c r="G51" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H51" s="2">
         <v>30</v>
       </c>
       <c r="I51" s="2">
-        <v>0</v>
-      </c>
-      <c r="J51" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K51" s="2" t="s">
         <v>15</v>
@@ -2439,25 +2439,25 @@
         <v>13</v>
       </c>
       <c r="D52" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E52" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F52" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G52" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H52" s="2">
         <v>30</v>
       </c>
       <c r="I52" s="2">
-        <v>30</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J52" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>15</v>
@@ -2471,16 +2471,16 @@
         <v>12</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D53" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E53" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F53" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G53" s="2">
         <v>30</v>
@@ -2500,31 +2500,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D54" s="2">
-        <v>10389</v>
+        <v>9449</v>
       </c>
       <c r="E54" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F54" s="2">
-        <v>-8137</v>
+        <v>-9076</v>
       </c>
       <c r="G54" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H54" s="2">
         <v>30</v>
       </c>
       <c r="I54" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J54" s="5" t="s">
         <v>35</v>
@@ -2541,28 +2541,28 @@
         <v>12</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>31</v>
+        <v>17</v>
       </c>
       <c r="D55" s="2">
-        <v>9487</v>
+        <v>9774</v>
       </c>
       <c r="E55" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F55" s="2">
-        <v>-9039</v>
+        <v>-8751</v>
       </c>
       <c r="G55" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2">
         <v>30</v>
       </c>
       <c r="I55" s="2">
-        <v>10</v>
-      </c>
-      <c r="J55" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K55" s="2" t="s">
         <v>15</v>
@@ -2579,25 +2579,25 @@
         <v>13</v>
       </c>
       <c r="D56" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E56" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F56" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G56" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H56" s="2">
         <v>30</v>
       </c>
       <c r="I56" s="2">
-        <v>30</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J56" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K56" s="2" t="s">
         <v>15</v>
@@ -2611,16 +2611,16 @@
         <v>12</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D57" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E57" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F57" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G57" s="2">
         <v>30</v>
@@ -2640,31 +2640,31 @@
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D58" s="2">
-        <v>10389</v>
+        <v>9525</v>
       </c>
       <c r="E58" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F58" s="2">
-        <v>-8137</v>
+        <v>-9000</v>
       </c>
       <c r="G58" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H58" s="2">
         <v>30</v>
       </c>
       <c r="I58" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J58" s="5" t="s">
         <v>35</v>
@@ -2681,25 +2681,25 @@
         <v>12</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D59" s="2">
-        <v>9564</v>
+        <v>10006</v>
       </c>
       <c r="E59" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F59" s="2">
-        <v>-8962</v>
+        <v>-8519</v>
       </c>
       <c r="G59" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H59" s="2">
         <v>30</v>
       </c>
       <c r="I59" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J59" s="5" t="s">
         <v>35</v>
@@ -2716,13 +2716,13 @@
         <v>12</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D60" s="2">
-        <v>10007</v>
+        <v>10006</v>
       </c>
       <c r="E60" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F60" s="2">
         <v>-8519</v>
@@ -2754,13 +2754,13 @@
         <v>21</v>
       </c>
       <c r="D61" s="2">
-        <v>10007</v>
+        <v>11044</v>
       </c>
       <c r="E61" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F61" s="2">
-        <v>-8519</v>
+        <v>-7481</v>
       </c>
       <c r="G61" s="2">
         <v>30</v>
@@ -2780,34 +2780,34 @@
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D62" s="2">
-        <v>11044</v>
+        <v>9774</v>
       </c>
       <c r="E62" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F62" s="2">
-        <v>-7482</v>
+        <v>-8751</v>
       </c>
       <c r="G62" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H62" s="2">
         <v>30</v>
       </c>
       <c r="I62" s="2">
-        <v>0</v>
-      </c>
-      <c r="J62" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J62" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>15</v>
@@ -2824,25 +2824,25 @@
         <v>13</v>
       </c>
       <c r="D63" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E63" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F63" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G63" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H63" s="2">
         <v>30</v>
       </c>
       <c r="I63" s="2">
-        <v>30</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J63" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>15</v>
@@ -2856,16 +2856,16 @@
         <v>12</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D64" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E64" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F64" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G64" s="2">
         <v>30</v>
@@ -2885,34 +2885,34 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D65" s="2">
-        <v>10389</v>
+        <v>9774</v>
       </c>
       <c r="E65" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F65" s="2">
-        <v>-8137</v>
+        <v>-8751</v>
       </c>
       <c r="G65" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H65" s="2">
         <v>30</v>
       </c>
       <c r="I65" s="2">
-        <v>0</v>
-      </c>
-      <c r="J65" s="5" t="s">
-        <v>35</v>
+        <v>30</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>15</v>
@@ -2929,25 +2929,25 @@
         <v>13</v>
       </c>
       <c r="D66" s="2">
-        <v>9775</v>
+        <v>10006</v>
       </c>
       <c r="E66" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F66" s="2">
-        <v>-8751</v>
+        <v>-8519</v>
       </c>
       <c r="G66" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H66" s="2">
         <v>30</v>
       </c>
       <c r="I66" s="2">
-        <v>30</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J66" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K66" s="2" t="s">
         <v>15</v>
@@ -2961,16 +2961,16 @@
         <v>12</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D67" s="2">
-        <v>10007</v>
+        <v>10389</v>
       </c>
       <c r="E67" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F67" s="2">
-        <v>-8519</v>
+        <v>-8136</v>
       </c>
       <c r="G67" s="2">
         <v>30</v>
@@ -2990,31 +2990,31 @@
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D68" s="2">
-        <v>10389</v>
+        <v>7194</v>
       </c>
       <c r="E68" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F68" s="2">
-        <v>-8137</v>
+        <v>-11331</v>
       </c>
       <c r="G68" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
         <v>30</v>
       </c>
       <c r="I68" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J68" s="5" t="s">
         <v>35</v>
@@ -3031,25 +3031,25 @@
         <v>12</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D69" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E69" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F69" s="2">
-        <v>-11332</v>
+        <v>-10885</v>
       </c>
       <c r="G69" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H69" s="2">
         <v>30</v>
       </c>
       <c r="I69" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J69" s="5" t="s">
         <v>35</v>
@@ -3066,25 +3066,25 @@
         <v>12</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D70" s="2">
-        <v>7671</v>
+        <v>8054</v>
       </c>
       <c r="E70" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F70" s="2">
-        <v>-10855</v>
+        <v>-10471</v>
       </c>
       <c r="G70" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H70" s="2">
         <v>30</v>
       </c>
       <c r="I70" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J70" s="5" t="s">
         <v>35</v>
@@ -3101,16 +3101,16 @@
         <v>12</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D71" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E71" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F71" s="2">
-        <v>-10472</v>
+        <v>-9979</v>
       </c>
       <c r="G71" s="2">
         <v>30</v>
@@ -3130,31 +3130,31 @@
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D72" s="2">
-        <v>8546</v>
+        <v>7717</v>
       </c>
       <c r="E72" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F72" s="2">
-        <v>-9980</v>
+        <v>-10808</v>
       </c>
       <c r="G72" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H72" s="2">
         <v>30</v>
       </c>
       <c r="I72" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J72" s="5" t="s">
         <v>35</v>
@@ -3171,25 +3171,25 @@
         <v>12</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D73" s="2">
-        <v>7748</v>
+        <v>8054</v>
       </c>
       <c r="E73" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F73" s="2">
-        <v>-10778</v>
+        <v>-10471</v>
       </c>
       <c r="G73" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2">
         <v>30</v>
       </c>
       <c r="I73" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J73" s="5" t="s">
         <v>35</v>
@@ -3206,16 +3206,16 @@
         <v>12</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D74" s="2">
         <v>8054</v>
       </c>
       <c r="E74" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F74" s="2">
-        <v>-10472</v>
+        <v>-10471</v>
       </c>
       <c r="G74" s="2">
         <v>30</v>
@@ -3244,13 +3244,13 @@
         <v>21</v>
       </c>
       <c r="D75" s="2">
-        <v>8054</v>
+        <v>10389</v>
       </c>
       <c r="E75" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F75" s="2">
-        <v>-10472</v>
+        <v>-8136</v>
       </c>
       <c r="G75" s="2">
         <v>30</v>
@@ -3270,31 +3270,31 @@
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D76" s="2">
-        <v>10389</v>
+        <v>7194</v>
       </c>
       <c r="E76" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F76" s="2">
-        <v>-8137</v>
+        <v>-11331</v>
       </c>
       <c r="G76" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H76" s="2">
         <v>30</v>
       </c>
       <c r="I76" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J76" s="5" t="s">
         <v>35</v>
@@ -3314,22 +3314,22 @@
         <v>13</v>
       </c>
       <c r="D77" s="2">
-        <v>7194</v>
+        <v>8054</v>
       </c>
       <c r="E77" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F77" s="2">
-        <v>-11332</v>
+        <v>-10471</v>
       </c>
       <c r="G77" s="2">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H77" s="2">
         <v>30</v>
       </c>
       <c r="I77" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="J77" s="5" t="s">
         <v>35</v>
@@ -3346,16 +3346,16 @@
         <v>12</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D78" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E78" s="2">
-        <v>18526</v>
+        <v>18525</v>
       </c>
       <c r="F78" s="2">
-        <v>-10472</v>
+        <v>-9979</v>
       </c>
       <c r="G78" s="2">
         <v>30</v>
@@ -3375,22 +3375,22 @@
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D79" s="2">
-        <v>8546</v>
+        <v>8054</v>
       </c>
       <c r="E79" s="2">
-        <v>18526</v>
+        <v>9556</v>
       </c>
       <c r="F79" s="2">
-        <v>-9980</v>
+        <v>-1502</v>
       </c>
       <c r="G79" s="2">
         <v>30</v>
@@ -3401,8 +3401,8 @@
       <c r="I79" s="2">
         <v>0</v>
       </c>
-      <c r="J79" s="5" t="s">
-        <v>35</v>
+      <c r="J79" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K79" s="2" t="s">
         <v>15</v>
@@ -3416,16 +3416,16 @@
         <v>12</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D80" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E80" s="2">
         <v>9556</v>
       </c>
       <c r="F80" s="2">
-        <v>-1502</v>
+        <v>-1010</v>
       </c>
       <c r="G80" s="2">
         <v>30</v>
@@ -3436,8 +3436,8 @@
       <c r="I80" s="2">
         <v>0</v>
       </c>
-      <c r="J80" s="4" t="s">
-        <v>17</v>
+      <c r="J80" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K80" s="2" t="s">
         <v>15</v>
@@ -3445,34 +3445,34 @@
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D81" s="2">
-        <v>8546</v>
+        <v>7640</v>
       </c>
       <c r="E81" s="2">
         <v>9556</v>
       </c>
       <c r="F81" s="2">
-        <v>-1010</v>
+        <v>-1916</v>
       </c>
       <c r="G81" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H81" s="2">
         <v>30</v>
       </c>
       <c r="I81" s="2">
-        <v>0</v>
-      </c>
-      <c r="J81" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K81" s="2" t="s">
         <v>15</v>
@@ -3486,28 +3486,28 @@
         <v>12</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="D82" s="2">
-        <v>7671</v>
+        <v>8054</v>
       </c>
       <c r="E82" s="2">
         <v>9556</v>
       </c>
       <c r="F82" s="2">
-        <v>-1885</v>
+        <v>-1502</v>
       </c>
       <c r="G82" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H82" s="2">
         <v>30</v>
       </c>
       <c r="I82" s="2">
-        <v>10</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>15</v>
@@ -3521,16 +3521,16 @@
         <v>12</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D83" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E83" s="2">
         <v>9556</v>
       </c>
       <c r="F83" s="2">
-        <v>-1502</v>
+        <v>-1010</v>
       </c>
       <c r="G83" s="2">
         <v>30</v>
@@ -3541,8 +3541,8 @@
       <c r="I83" s="2">
         <v>0</v>
       </c>
-      <c r="J83" s="4" t="s">
-        <v>17</v>
+      <c r="J83" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>15</v>
@@ -3550,34 +3550,34 @@
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="D84" s="2">
-        <v>8546</v>
+        <v>7717</v>
       </c>
       <c r="E84" s="2">
         <v>9556</v>
       </c>
       <c r="F84" s="2">
-        <v>-1010</v>
+        <v>-1839</v>
       </c>
       <c r="G84" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H84" s="2">
         <v>30</v>
       </c>
       <c r="I84" s="2">
-        <v>0</v>
-      </c>
-      <c r="J84" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>15</v>
@@ -3591,28 +3591,28 @@
         <v>12</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="D85" s="2">
-        <v>7748</v>
+        <v>8054</v>
       </c>
       <c r="E85" s="2">
         <v>9556</v>
       </c>
       <c r="F85" s="2">
-        <v>-1808</v>
+        <v>-1502</v>
       </c>
       <c r="G85" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H85" s="2">
         <v>30</v>
       </c>
       <c r="I85" s="2">
-        <v>10</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>17</v>
+        <v>0</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K85" s="2" t="s">
         <v>15</v>
@@ -3626,7 +3626,7 @@
         <v>12</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D86" s="2">
         <v>8054</v>
@@ -3646,8 +3646,8 @@
       <c r="I86" s="2">
         <v>0</v>
       </c>
-      <c r="J86" s="4" t="s">
-        <v>17</v>
+      <c r="J86" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K86" s="2" t="s">
         <v>15</v>
@@ -3664,13 +3664,13 @@
         <v>21</v>
       </c>
       <c r="D87" s="2">
-        <v>8054</v>
+        <v>9542</v>
       </c>
       <c r="E87" s="2">
         <v>9556</v>
       </c>
       <c r="F87" s="2">
-        <v>-1502</v>
+        <v>-14</v>
       </c>
       <c r="G87" s="2">
         <v>30</v>
@@ -3681,8 +3681,8 @@
       <c r="I87" s="2">
         <v>0</v>
       </c>
-      <c r="J87" s="4" t="s">
-        <v>17</v>
+      <c r="J87" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>15</v>
@@ -3690,22 +3690,22 @@
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="D88" s="2">
-        <v>9542</v>
+        <v>8054</v>
       </c>
       <c r="E88" s="2">
-        <v>9556</v>
+        <v>10553</v>
       </c>
       <c r="F88" s="2">
-        <v>-14</v>
+        <v>-2499</v>
       </c>
       <c r="G88" s="2">
         <v>30</v>
@@ -3716,8 +3716,8 @@
       <c r="I88" s="2">
         <v>0</v>
       </c>
-      <c r="J88" s="4" t="s">
-        <v>17</v>
+      <c r="J88" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K88" s="2" t="s">
         <v>15</v>
@@ -3731,16 +3731,16 @@
         <v>12</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D89" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E89" s="2">
         <v>10553</v>
       </c>
       <c r="F89" s="2">
-        <v>-2499</v>
+        <v>-2007</v>
       </c>
       <c r="G89" s="2">
         <v>30</v>
@@ -3751,8 +3751,8 @@
       <c r="I89" s="2">
         <v>0</v>
       </c>
-      <c r="J89" s="4" t="s">
-        <v>17</v>
+      <c r="J89" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K89" s="2" t="s">
         <v>15</v>
@@ -3760,22 +3760,22 @@
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D90" s="2">
-        <v>8546</v>
+        <v>8054</v>
       </c>
       <c r="E90" s="2">
-        <v>10553</v>
+        <v>9556</v>
       </c>
       <c r="F90" s="2">
-        <v>-2007</v>
+        <v>-1502</v>
       </c>
       <c r="G90" s="2">
         <v>30</v>
@@ -3786,8 +3786,8 @@
       <c r="I90" s="2">
         <v>0</v>
       </c>
-      <c r="J90" s="4" t="s">
-        <v>17</v>
+      <c r="J90" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K90" s="2" t="s">
         <v>15</v>
@@ -3801,16 +3801,16 @@
         <v>12</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D91" s="2">
-        <v>8054</v>
+        <v>8546</v>
       </c>
       <c r="E91" s="2">
         <v>9556</v>
       </c>
       <c r="F91" s="2">
-        <v>-1502</v>
+        <v>-1010</v>
       </c>
       <c r="G91" s="2">
         <v>30</v>
@@ -3821,8 +3821,8 @@
       <c r="I91" s="2">
         <v>0</v>
       </c>
-      <c r="J91" s="4" t="s">
-        <v>17</v>
+      <c r="J91" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K91" s="2" t="s">
         <v>15</v>
@@ -3830,34 +3830,34 @@
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D92" s="2">
-        <v>8546</v>
+        <v>7194</v>
       </c>
       <c r="E92" s="2">
-        <v>9556</v>
+        <v>23017</v>
       </c>
       <c r="F92" s="2">
-        <v>-1010</v>
+        <v>-15823</v>
       </c>
       <c r="G92" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H92" s="2">
         <v>30</v>
       </c>
       <c r="I92" s="2">
-        <v>0</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>17</v>
+        <v>30</v>
+      </c>
+      <c r="J92" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K92" s="2" t="s">
         <v>15</v>
@@ -3871,25 +3871,25 @@
         <v>12</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D93" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E93" s="2">
         <v>23017</v>
       </c>
       <c r="F93" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G93" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H93" s="2">
         <v>30</v>
       </c>
       <c r="I93" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J93" s="5" t="s">
         <v>35</v>
@@ -3906,28 +3906,28 @@
         <v>12</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D94" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E94" s="2">
         <v>23017</v>
       </c>
       <c r="F94" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G94" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H94" s="2">
         <v>30</v>
       </c>
       <c r="I94" s="2">
-        <v>10</v>
-      </c>
-      <c r="J94" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J94" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K94" s="2" t="s">
         <v>15</v>
@@ -3935,34 +3935,34 @@
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="B95" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D95" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E95" s="2">
         <v>23017</v>
       </c>
       <c r="F95" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G95" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H95" s="2">
         <v>30</v>
       </c>
       <c r="I95" s="2">
-        <v>0</v>
-      </c>
-      <c r="J95" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J95" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K95" s="2" t="s">
         <v>15</v>
@@ -3976,25 +3976,25 @@
         <v>12</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D96" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E96" s="2">
         <v>23017</v>
       </c>
       <c r="F96" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G96" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H96" s="2">
         <v>30</v>
       </c>
       <c r="I96" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J96" s="5" t="s">
         <v>35</v>
@@ -4011,28 +4011,28 @@
         <v>12</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D97" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E97" s="2">
         <v>23017</v>
       </c>
       <c r="F97" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G97" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H97" s="2">
         <v>30</v>
       </c>
       <c r="I97" s="2">
-        <v>10</v>
-      </c>
-      <c r="J97" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J97" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K97" s="2" t="s">
         <v>15</v>
@@ -4040,34 +4040,34 @@
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D98" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E98" s="2">
         <v>23017</v>
       </c>
       <c r="F98" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G98" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H98" s="2">
         <v>30</v>
       </c>
       <c r="I98" s="2">
-        <v>0</v>
-      </c>
-      <c r="J98" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J98" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>15</v>
@@ -4081,25 +4081,25 @@
         <v>12</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D99" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E99" s="2">
         <v>23017</v>
       </c>
       <c r="F99" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G99" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H99" s="2">
         <v>30</v>
       </c>
       <c r="I99" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J99" s="5" t="s">
         <v>35</v>
@@ -4116,28 +4116,28 @@
         <v>12</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D100" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E100" s="2">
         <v>23017</v>
       </c>
       <c r="F100" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G100" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H100" s="2">
         <v>30</v>
       </c>
       <c r="I100" s="2">
-        <v>10</v>
-      </c>
-      <c r="J100" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J100" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>15</v>
@@ -4145,34 +4145,34 @@
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B101" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D101" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E101" s="2">
         <v>23017</v>
       </c>
       <c r="F101" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G101" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H101" s="2">
         <v>30</v>
       </c>
       <c r="I101" s="2">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J101" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K101" s="2" t="s">
         <v>15</v>
@@ -4186,25 +4186,25 @@
         <v>12</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D102" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E102" s="2">
         <v>23017</v>
       </c>
       <c r="F102" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G102" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H102" s="2">
         <v>30</v>
       </c>
       <c r="I102" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J102" s="5" t="s">
         <v>35</v>
@@ -4221,28 +4221,28 @@
         <v>12</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D103" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E103" s="2">
         <v>23017</v>
       </c>
       <c r="F103" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G103" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H103" s="2">
         <v>30</v>
       </c>
       <c r="I103" s="2">
-        <v>10</v>
-      </c>
-      <c r="J103" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J103" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>15</v>
@@ -4250,34 +4250,34 @@
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B104" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D104" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E104" s="2">
         <v>23017</v>
       </c>
       <c r="F104" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G104" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H104" s="2">
         <v>30</v>
       </c>
       <c r="I104" s="2">
-        <v>0</v>
-      </c>
-      <c r="J104" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J104" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K104" s="2" t="s">
         <v>15</v>
@@ -4291,25 +4291,25 @@
         <v>12</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D105" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E105" s="2">
         <v>23017</v>
       </c>
       <c r="F105" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G105" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H105" s="2">
         <v>30</v>
       </c>
       <c r="I105" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J105" s="5" t="s">
         <v>35</v>
@@ -4326,28 +4326,28 @@
         <v>12</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D106" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E106" s="2">
         <v>23017</v>
       </c>
       <c r="F106" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G106" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H106" s="2">
         <v>30</v>
       </c>
       <c r="I106" s="2">
-        <v>10</v>
-      </c>
-      <c r="J106" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J106" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K106" s="2" t="s">
         <v>15</v>
@@ -4355,34 +4355,34 @@
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B107" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D107" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E107" s="2">
         <v>23017</v>
       </c>
       <c r="F107" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G107" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H107" s="2">
         <v>30</v>
       </c>
       <c r="I107" s="2">
-        <v>0</v>
-      </c>
-      <c r="J107" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J107" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K107" s="2" t="s">
         <v>15</v>
@@ -4396,25 +4396,25 @@
         <v>12</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D108" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E108" s="2">
         <v>23017</v>
       </c>
       <c r="F108" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G108" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H108" s="2">
         <v>30</v>
       </c>
       <c r="I108" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J108" s="5" t="s">
         <v>35</v>
@@ -4431,28 +4431,28 @@
         <v>12</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D109" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E109" s="2">
         <v>23017</v>
       </c>
       <c r="F109" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G109" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H109" s="2">
         <v>30</v>
       </c>
       <c r="I109" s="2">
-        <v>10</v>
-      </c>
-      <c r="J109" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J109" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K109" s="2" t="s">
         <v>15</v>
@@ -4460,34 +4460,34 @@
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D110" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E110" s="2">
         <v>23017</v>
       </c>
       <c r="F110" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G110" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H110" s="2">
         <v>30</v>
       </c>
       <c r="I110" s="2">
-        <v>0</v>
-      </c>
-      <c r="J110" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J110" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>15</v>
@@ -4501,25 +4501,25 @@
         <v>12</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D111" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E111" s="2">
         <v>23017</v>
       </c>
       <c r="F111" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G111" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H111" s="2">
         <v>30</v>
       </c>
       <c r="I111" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J111" s="5" t="s">
         <v>35</v>
@@ -4536,28 +4536,28 @@
         <v>12</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D112" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E112" s="2">
         <v>23017</v>
       </c>
       <c r="F112" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G112" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H112" s="2">
         <v>30</v>
       </c>
       <c r="I112" s="2">
-        <v>10</v>
-      </c>
-      <c r="J112" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J112" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K112" s="2" t="s">
         <v>15</v>
@@ -4565,34 +4565,34 @@
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B113" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D113" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E113" s="2">
         <v>23017</v>
       </c>
       <c r="F113" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G113" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H113" s="2">
         <v>30</v>
       </c>
       <c r="I113" s="2">
-        <v>0</v>
-      </c>
-      <c r="J113" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J113" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K113" s="2" t="s">
         <v>15</v>
@@ -4606,25 +4606,25 @@
         <v>12</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D114" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E114" s="2">
         <v>23017</v>
       </c>
       <c r="F114" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G114" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H114" s="2">
         <v>30</v>
       </c>
       <c r="I114" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J114" s="5" t="s">
         <v>35</v>
@@ -4641,28 +4641,28 @@
         <v>12</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D115" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E115" s="2">
         <v>23017</v>
       </c>
       <c r="F115" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G115" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H115" s="2">
         <v>30</v>
       </c>
       <c r="I115" s="2">
-        <v>10</v>
-      </c>
-      <c r="J115" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J115" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K115" s="2" t="s">
         <v>15</v>
@@ -4670,34 +4670,34 @@
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="B116" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="D116" s="2">
-        <v>19672</v>
+        <v>7194</v>
       </c>
       <c r="E116" s="2">
         <v>23017</v>
       </c>
       <c r="F116" s="2">
-        <v>-3345</v>
+        <v>-15823</v>
       </c>
       <c r="G116" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H116" s="2">
         <v>30</v>
       </c>
       <c r="I116" s="2">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="s">
-        <v>14</v>
+        <v>30</v>
+      </c>
+      <c r="J116" s="5" t="s">
+        <v>35</v>
       </c>
       <c r="K116" s="2" t="s">
         <v>15</v>
@@ -4711,25 +4711,25 @@
         <v>12</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>13</v>
+        <v>30</v>
       </c>
       <c r="D117" s="2">
-        <v>7194</v>
+        <v>7640</v>
       </c>
       <c r="E117" s="2">
         <v>23017</v>
       </c>
       <c r="F117" s="2">
-        <v>-15823</v>
+        <v>-15377</v>
       </c>
       <c r="G117" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H117" s="2">
         <v>30</v>
       </c>
       <c r="I117" s="2">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="J117" s="5" t="s">
         <v>35</v>
@@ -4746,65 +4746,30 @@
         <v>12</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D118" s="2">
-        <v>7671</v>
+        <v>19672</v>
       </c>
       <c r="E118" s="2">
         <v>23017</v>
       </c>
       <c r="F118" s="2">
-        <v>-15346</v>
+        <v>-3345</v>
       </c>
       <c r="G118" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H118" s="2">
         <v>30</v>
       </c>
       <c r="I118" s="2">
-        <v>10</v>
-      </c>
-      <c r="J118" s="5" t="s">
-        <v>35</v>
+        <v>0</v>
+      </c>
+      <c r="J118" s="4" t="s">
+        <v>18</v>
       </c>
       <c r="K118" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="119" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A119" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C119" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="D119" s="2">
-        <v>19672</v>
-      </c>
-      <c r="E119" s="2">
-        <v>23017</v>
-      </c>
-      <c r="F119" s="2">
-        <v>-3345</v>
-      </c>
-      <c r="G119" s="2">
-        <v>30</v>
-      </c>
-      <c r="H119" s="2">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2">
-        <v>0</v>
-      </c>
-      <c r="J119" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K119" s="2" t="s">
         <v>15</v>
       </c>
     </row>
